--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T10:29:33+00:00</t>
+    <t>2026-03-01T15:46:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T15:46:45+00:00</t>
+    <t>2026-03-02T16:20:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T16:20:44+00:00</t>
+    <t>2026-03-02T17:40:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T17:40:54+00:00</t>
+    <t>2026-03-03T16:09:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T16:09:57+00:00</t>
+    <t>2026-03-03T18:16:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T18:16:34+00:00</t>
+    <t>2026-03-03T20:10:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T20:10:31+00:00</t>
+    <t>2026-03-24T11:22:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -85,7 +85,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Maps observation codes to their expected UCUM units for the 'Other' observation profile.</t>
+    <t>Maps observation codes to their expected UCUM units for the 'Other Quantities' observation profile.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T11:22:25+00:00</t>
+    <t>2026-03-27T21:20:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T21:20:49+00:00</t>
+    <t>2026-03-29T11:39:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-29T11:39:37+00:00</t>
+    <t>2026-03-29T11:44:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-29T11:44:39+00:00</t>
+    <t>2026-04-03T14:50:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-03T14:50:23+00:00</t>
+    <t>2026-05-18T08:38:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T08:38:27+00:00</t>
+    <t>2026-05-18T10:23:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T10:23:40+00:00</t>
+    <t>2026-06-01T14:49:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T14:49:28+00:00</t>
+    <t>2026-06-03T09:07:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T09:07:40+00:00</t>
+    <t>2026-06-03T10:15:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T10:15:52+00:00</t>
+    <t>2026-06-16T06:28:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T06:28:21+00:00</t>
+    <t>2026-06-18T08:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T08:24:24+00:00</t>
+    <t>2026-06-18T13:26:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:26:12+00:00</t>
+    <t>2026-06-22T11:44:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T11:44:44+00:00</t>
+    <t>2026-06-22T12:35:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T12:35:22+00:00</t>
+    <t>2026-06-22T13:57:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T13:57:07+00:00</t>
+    <t>2026-06-22T14:44:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T14:44:05+00:00</t>
+    <t>2026-06-24T07:32:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T07:32:55+00:00</t>
+    <t>2026-06-24T12:07:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T12:07:10+00:00</t>
+    <t>2026-06-24T13:18:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T13:18:54+00:00</t>
+    <t>2026-06-29T10:23:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T10:23:22+00:00</t>
+    <t>2026-06-29T10:47:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T10:47:49+00:00</t>
+    <t>2026-06-29T16:58:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T16:58:51+00:00</t>
+    <t>2026-06-29T17:35:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:35:07+00:00</t>
+    <t>2026-06-30T08:18:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:18:50+00:00</t>
+    <t>2026-06-30T14:49:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T14:49:39+00:00</t>
+    <t>2026-07-01T08:47:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T08:47:20+00:00</t>
+    <t>2026-07-01T10:20:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T10:20:10+00:00</t>
+    <t>2026-07-22T09:38:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T09:38:36+00:00</t>
+    <t>2026-07-22T10:33:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T10:33:49+00:00</t>
+    <t>2026-07-22T11:37:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T11:37:23+00:00</t>
+    <t>2026-07-23T14:49:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T14:49:55+00:00</t>
+    <t>2026-08-05T12:17:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:17:57+00:00</t>
+    <t>2026-08-05T12:30:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:30:06+00:00</t>
+    <t>2026-08-06T10:54:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T10:54:53+00:00</t>
+    <t>2026-08-07T08:52:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T08:52:23+00:00</t>
+    <t>2026-08-13T06:23:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T06:23:48+00:00</t>
+    <t>2026-08-18T12:08:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T12:08:37+00:00</t>
+    <t>2026-08-18T12:35:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T12:35:51+00:00</t>
+    <t>2026-08-20T08:19:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T08:19:53+00:00</t>
+    <t>2026-08-20T13:42:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T13:42:02+00:00</t>
+    <t>2026-08-26T07:06:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T07:06:07+00:00</t>
+    <t>2026-08-26T07:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/AtPrenudgeCodeUnitMap.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T07:22:28+00:00</t>
+    <t>2026-08-26T07:28:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
